--- a/scenarios_def.xlsx
+++ b/scenarios_def.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/louissallard/Desktop/ETE/Optim_JULIA/Projet/EOD-Gaz/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F35EE55A-B0DF-2744-B56A-3DFB641F1274}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71A680A1-A646-7D40-AF35-E32706D234D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4300" yWindow="5580" windowWidth="26440" windowHeight="14880" xr2:uid="{EAC5DB97-9E6B-3142-9580-796EC73B4E6C}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="30">
   <si>
     <t>Scénario</t>
   </si>
@@ -68,9 +68,6 @@
     <t>Durée d'exécution (min)</t>
   </si>
   <si>
-    <t>AG=3, coûts variables gaz</t>
-  </si>
-  <si>
     <t>AG=3, pénalité écart à la moyenne stock CH4 = 100€/MWh</t>
   </si>
   <si>
@@ -123,6 +120,12 @@
   </si>
   <si>
     <t>hausse des prix ? --&gt; pas implémenté pour le moment</t>
+  </si>
+  <si>
+    <t>AG=3, coûts variables gaz import</t>
+  </si>
+  <si>
+    <t>avec  la modélisation de base du stock CH4 (sans point cible ou pénalité d'écart à la moyenne)</t>
   </si>
 </sst>
 </file>
@@ -172,11 +175,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1429,7 +1435,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CF727FC-8B84-324B-A620-74B7E6A8365F}">
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="48.83203125" customWidth="1"/>
@@ -1523,7 +1529,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="C8">
         <v>36.4</v>
@@ -1535,7 +1541,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C9">
         <v>31.65</v>
@@ -1547,7 +1553,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C10">
         <v>33.35</v>
@@ -1559,7 +1565,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C11">
         <v>29.37</v>
@@ -1571,7 +1577,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C12" t="s">
         <v>3</v>
@@ -1583,7 +1589,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C13" t="s">
         <v>3</v>
@@ -1595,7 +1601,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C14" t="s">
         <v>3</v>
@@ -1607,7 +1613,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C15">
         <v>33.880000000000003</v>
@@ -1619,130 +1625,138 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C16">
         <v>29.21</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C17">
         <v>24.73</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C18" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C19" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C20" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C21" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+        <v>27</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C22" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="2"/>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E22" s="3"/>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C23" t="s">
         <v>3</v>
       </c>
       <c r="D23" s="2"/>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E23" s="3"/>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C24" t="s">
         <v>3</v>
       </c>
       <c r="D24" s="2"/>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E24" s="3"/>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C25" t="s">
         <v>3</v>
       </c>
       <c r="D25" s="2"/>
+      <c r="E25" s="3"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="D21:D25"/>
+    <mergeCell ref="E21:E25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>

--- a/scenarios_def.xlsx
+++ b/scenarios_def.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/louissallard/Desktop/ETE/Optim_JULIA/Projet/EOD-Gaz/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71A680A1-A646-7D40-AF35-E32706D234D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4954A2CD-B837-2A49-9150-265707BF6E84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4300" yWindow="5580" windowWidth="26440" windowHeight="14880" xr2:uid="{EAC5DB97-9E6B-3142-9580-796EC73B4E6C}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="30">
   <si>
     <t>Scénario</t>
   </si>
@@ -175,7 +175,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -183,6 +183,13 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement i="0"/>
+        </ext>
+      </extLst>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1118,6 +1125,23 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/featurePropertyBag/featurePropertyBag.xml><?xml version="1.0" encoding="utf-8"?>
+<FeaturePropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag">
+  <bag type="Checkbox"/>
+  <bag type="XFControls">
+    <bagId k="CellControl">0</bagId>
+  </bag>
+  <bag type="XFComplement">
+    <bagId k="XFControls">1</bagId>
+  </bag>
+  <bag type="XFComplements" extRef="XFComplementsMapperExtRef">
+    <a k="MappedFeaturePropertyBags">
+      <bagId>2</bagId>
+    </a>
+  </bag>
+</FeaturePropertyBags>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
   <a:themeElements>
@@ -1663,8 +1687,8 @@
       <c r="B19" t="s">
         <v>20</v>
       </c>
-      <c r="C19" t="s">
-        <v>3</v>
+      <c r="C19" s="4" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
@@ -1675,8 +1699,8 @@
       <c r="B20" t="s">
         <v>21</v>
       </c>
-      <c r="C20" t="s">
-        <v>3</v>
+      <c r="C20" s="4" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
@@ -1687,8 +1711,8 @@
       <c r="B21" t="s">
         <v>22</v>
       </c>
-      <c r="C21" t="s">
-        <v>3</v>
+      <c r="C21" s="4" t="b">
+        <v>1</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>27</v>
@@ -1705,8 +1729,8 @@
       <c r="B22" t="s">
         <v>23</v>
       </c>
-      <c r="C22" t="s">
-        <v>3</v>
+      <c r="C22" s="4" t="b">
+        <v>1</v>
       </c>
       <c r="D22" s="2"/>
       <c r="E22" s="3"/>
@@ -1719,8 +1743,8 @@
       <c r="B23" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C23" t="s">
-        <v>3</v>
+      <c r="C23" s="4" t="b">
+        <v>1</v>
       </c>
       <c r="D23" s="2"/>
       <c r="E23" s="3"/>
@@ -1733,8 +1757,8 @@
       <c r="B24" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C24" t="s">
-        <v>3</v>
+      <c r="C24" s="4" t="b">
+        <v>1</v>
       </c>
       <c r="D24" s="2"/>
       <c r="E24" s="3"/>
@@ -1747,8 +1771,8 @@
       <c r="B25" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C25" t="s">
-        <v>3</v>
+      <c r="C25" s="4" t="b">
+        <v>1</v>
       </c>
       <c r="D25" s="2"/>
       <c r="E25" s="3"/>

--- a/scenarios_def.xlsx
+++ b/scenarios_def.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/louissallard/Desktop/ETE/Optim_JULIA/Projet/EOD-Gaz/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4954A2CD-B837-2A49-9150-265707BF6E84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4931D066-3A30-F14C-AFEE-51323B586F4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4300" yWindow="5580" windowWidth="26440" windowHeight="14880" xr2:uid="{EAC5DB97-9E6B-3142-9580-796EC73B4E6C}"/>
   </bookViews>

--- a/scenarios_def.xlsx
+++ b/scenarios_def.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/louissallard/Desktop/ETE/Optim_JULIA/Projet/EOD-Gaz/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4931D066-3A30-F14C-AFEE-51323B586F4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF7C769E-2223-CD4D-A9B3-50A5BCDB4FD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4300" yWindow="5580" windowWidth="26440" windowHeight="14880" xr2:uid="{EAC5DB97-9E6B-3142-9580-796EC73B4E6C}"/>
+    <workbookView xWindow="3880" yWindow="2640" windowWidth="26440" windowHeight="14880" xr2:uid="{EAC5DB97-9E6B-3142-9580-796EC73B4E6C}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -178,18 +178,18 @@
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
           <xfpb:xfComplement i="0"/>
         </ext>
       </extLst>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1687,7 +1687,7 @@
       <c r="B19" t="s">
         <v>20</v>
       </c>
-      <c r="C19" s="4" t="b">
+      <c r="C19" s="2" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1699,8 +1699,8 @@
       <c r="B20" t="s">
         <v>21</v>
       </c>
-      <c r="C20" s="4" t="b">
-        <v>0</v>
+      <c r="C20" s="2" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
@@ -1711,13 +1711,13 @@
       <c r="B21" t="s">
         <v>22</v>
       </c>
-      <c r="C21" s="4" t="b">
+      <c r="C21" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="D21" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E21" s="3" t="s">
+      <c r="E21" s="4" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1729,11 +1729,11 @@
       <c r="B22" t="s">
         <v>23</v>
       </c>
-      <c r="C22" s="4" t="b">
+      <c r="C22" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="D22" s="2"/>
-      <c r="E22" s="3"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="4"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23">
@@ -1743,11 +1743,11 @@
       <c r="B23" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C23" s="4" t="b">
+      <c r="C23" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="D23" s="2"/>
-      <c r="E23" s="3"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="4"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24">
@@ -1757,11 +1757,11 @@
       <c r="B24" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C24" s="4" t="b">
+      <c r="C24" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="D24" s="2"/>
-      <c r="E24" s="3"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="4"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25">
@@ -1771,11 +1771,11 @@
       <c r="B25" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C25" s="4" t="b">
+      <c r="C25" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="D25" s="2"/>
-      <c r="E25" s="3"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="2">
